--- a/merged_orders/merged_跨8.xlsx
+++ b/merged_orders/merged_跨8.xlsx
@@ -429,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>下单件数</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SKU ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>产品名称</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -476,18 +476,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>关节凝胶</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.730943065166418e+18</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>关节凝胶</t>
+          <t>1730943065166418235</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -524,18 +526,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>足贴</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.732140184357475e+18</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>足贴</t>
+          <t>1732140184357474619</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
